--- a/后端/paletteseek_backend/palette_results.xlsx
+++ b/后端/paletteseek_backend/palette_results.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS101"/>
+  <dimension ref="A1:AS125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,8 +657,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>869</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -727,22 +729,22 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>灰色、深橙色、黑色、灰色、深橙色、深黄色、黄色、灰黄色、灰橙色</t>
+          <t>灰色、深棕色、近黑色、灰色、深棕色、深棕色、深黄色、黄色、浅灰色</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>灰色、深橙色、黑色、灰色、深橙色、深黄色、黄色、灰黄色、灰橙色、深色调、橙色系</t>
+          <t>灰色、深棕色、近黑色、灰色、深棕色、深棕色、深黄色、黄色、浅灰色</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -882,8 +884,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2189</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2189</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -952,7 +956,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>浅蓝色、白色、浅红色、深灰色、深灰色、蓝色、浅灰色、灰粉紫色、红色</t>
+          <t>天蓝色、白色、浅橙色、近黑色、灰色、蓝色、浅灰色、灰红色、鲜红色</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -962,12 +966,12 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>蓝色系</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>浅蓝色、白色、浅红色、深灰色、深灰色、蓝色、浅灰色、灰粉紫色、红色、中明度色调、灰色系</t>
+          <t>天蓝色、白色、浅橙色、近黑色、灰色、蓝色、浅灰色、灰红色、鲜红色</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1107,8 +1111,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2816</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2816</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1177,7 +1183,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>橙色、橙色、灰黄色、橙色、橙色、灰青色、青色、青色、浅灰色</t>
+          <t>亮橙色、橙色、浅灰色、金黄色、暗橙色、浅灰青色、蓝绿色、青色、浅灰色</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1192,7 +1198,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>橙色、橙色、灰黄色、橙色、橙色、灰青色、青色、青色、浅灰色、中明度色调、橙色系</t>
+          <t>亮橙色、橙色、浅灰色、金黄色、暗橙色、浅灰青色、蓝绿色、青色、浅灰色</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1332,8 +1338,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>4081</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4081</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1402,22 +1410,22 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>黑色、灰橙色、灰橙色、灰黄色、深橙色、橙色、深橙色、橙色、橙色</t>
+          <t>近黑色、灰色、深灰棕色、灰色、深棕色、亮橙色、深棕色、亮橙色、橙红色</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>低饱和色调</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>黑色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>黑色、灰橙色、灰橙色、灰黄色、深橙色、橙色、深橙色、橙色、橙色、深色调、黑色系</t>
+          <t>近黑色、灰色、深灰棕色、灰色、深棕色、亮橙色、深棕色、亮橙色、橙红色</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1557,8 +1565,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4428</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4428</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1627,7 +1637,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>深橙色、黑色、深橙色、深橙色、黑色、深橙色、深橙色、橙色、橙色</t>
+          <t>深棕色、近黑色、深棕色、深棕色、深棕色、深暗橙色、深棕色、橙色、亮橙色</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1637,12 +1647,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>深橙色、黑色、深橙色、深橙色、黑色、深橙色、深橙色、橙色、橙色、深色调、橙色系</t>
+          <t>深棕色、近黑色、深棕色、深棕色、深棕色、深暗橙色、深棕色、橙色、亮橙色</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1782,8 +1792,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>4575</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4575</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1852,22 +1864,22 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、深橙色、深橙色、橙色、橙色、橙色、橙色、橙色</t>
+          <t>深棕色、深灰棕色、深棕色、深棕色、亮橙色、橙色、浅橙红色、亮橙色、橙色</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、深橙色、深橙色、橙色、橙色、橙色、橙色、橙色、深色调、橙色系</t>
+          <t>深棕色、深灰棕色、深棕色、深棕色、亮橙色、橙色、浅橙红色、亮橙色、橙色</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -2007,8 +2019,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>4758</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2077,22 +2091,22 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、黑色、橙色、灰色、灰蓝色、灰色、橙色、浅灰色</t>
+          <t>深棕色、深棕色、深棕色、黄色、灰色、灰青色、灰色、黄色、浅灰色</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、黑色、橙色、灰色、灰蓝色、灰色、橙色、浅灰色、中明度色调、橙色系</t>
+          <t>深棕色、深棕色、深棕色、黄色、灰色、灰青色、灰色、黄色、浅灰色</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -2232,8 +2246,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>4773</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>4773</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2302,7 +2318,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>深红色、深橙色、橙色、橙色、橙色、橙色、橙色、黑色、浅橙色</t>
+          <t>深暗红色、深暗橙色、橙色、亮橙色、亮橙色、橙色、浅橙红色、深棕色、浅米黄色</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2317,7 +2333,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>深红色、深橙色、橙色、橙色、橙色、橙色、橙色、黑色、浅橙色、中明度色调、橙色系</t>
+          <t>深暗红色、深暗橙色、橙色、亮橙色、亮橙色、橙色、浅橙红色、深棕色、浅米黄色</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -2457,8 +2473,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>4788</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4788</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2527,7 +2545,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>橙色、深橙色、橙色、深橙色、灰橙色、橙色、浅橙色、橙色、灰橙色</t>
+          <t>深黄色、深棕色、黄色、深暗橙色、亮橙色、亮橙色、浅灰色、金黄色、灰色</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2537,12 +2555,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>橙色、深橙色、橙色、深橙色、灰橙色、橙色、浅橙色、橙色、灰橙色、中明度色调、橙色系</t>
+          <t>深黄色、深棕色、黄色、深暗橙色、亮橙色、亮橙色、浅灰色、金黄色、灰色</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -2682,8 +2700,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>4796</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>4796</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2752,7 +2772,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>深橙色、橙色、橙色、橙色、橙色、浅橙色、深橙色、灰蓝色、灰色</t>
+          <t>深棕色、橙色、亮橙色、橙色、橙红色、浅柠檬黄、深棕色、灰青色、灰色</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2767,7 +2787,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>深橙色、橙色、橙色、橙色、橙色、浅橙色、深橙色、灰蓝色、灰色、中明度色调、橙色系</t>
+          <t>深棕色、橙色、亮橙色、橙色、橙红色、浅柠檬黄、深棕色、灰青色、灰色</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -2907,8 +2927,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>4884</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>4884</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2977,7 +2999,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>黑色、深蓝色、黑色、深灰色、灰橙色、灰橙色、深蓝色、灰橙色、浅橙色</t>
+          <t>深藏蓝色、深藏蓝色、近黑色、灰色、深灰棕色、灰色、深藏蓝色、灰色、浅灰色</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2987,12 +3009,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>黑色系</t>
+          <t>蓝色系</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>黑色、深蓝色、黑色、深灰色、灰橙色、灰橙色、深蓝色、灰橙色、浅橙色、深色调、黑色系</t>
+          <t>深藏蓝色、深藏蓝色、近黑色、灰色、深灰棕色、灰色、深藏蓝色、灰色、浅灰色</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -3132,8 +3154,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>5357</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -3202,7 +3226,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>紫色、红色、深红色、绿色、浅黄色、浅橙色、白色、浅红色、浅灰色</t>
+          <t>鲜紫色、红色、深灰棕色、绿色、浅米黄色、柠檬黄、白色、玫瑰红、浅灰色</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -3217,7 +3241,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>紫色、红色、深红色、绿色、浅黄色、浅橙色、白色、浅红色、浅灰色、中明度色调、红色系</t>
+          <t>鲜紫色、红色、深灰棕色、绿色、浅米黄色、柠檬黄、白色、玫瑰红、浅灰色</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -3357,8 +3381,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>5848</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5848</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3427,22 +3453,22 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>深橙色、黑色、深橙色、橙色、蓝色、橙色、浅灰色、灰蓝色、橙色</t>
+          <t>深棕色、深棕色、深暗橙色、橙色、浅天蓝色、橙色、浅灰色、钴蓝色、亮橙色</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>深橙色、黑色、深橙色、橙色、蓝色、橙色、浅灰色、灰蓝色、橙色、中明度色调、橙色系</t>
+          <t>深棕色、深棕色、深暗橙色、橙色、浅天蓝色、橙色、浅灰色、钴蓝色、亮橙色</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -3582,8 +3608,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>6565</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6565</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3652,12 +3680,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>黑色、灰色、深橙色、橙色、橙色、灰橙色、橙色、深橙色、浅橙色</t>
+          <t>近黑色、浅灰色、深暗橙色、浅柠檬黄、橙色、黄色、亮橙色、深棕色、浅柠檬黄</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -3667,7 +3695,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>黑色、灰色、深橙色、橙色、橙色、灰橙色、橙色、深橙色、浅橙色、中明度色调、橙色系</t>
+          <t>近黑色、浅灰色、深暗橙色、浅柠檬黄、橙色、黄色、亮橙色、深棕色、浅柠檬黄</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -3807,8 +3835,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>7021</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7021</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3877,22 +3907,22 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>黑色、深灰色、灰蓝色、深青色、橙色、橙色、浅灰色、灰色、浅黄色</t>
+          <t>近黑色、灰色、蓝色、深暗青色、橙色、亮橙色、浅灰色、浅灰色、浅米黄色</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>低饱和色调</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>橙色系</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>黑色、深灰色、灰蓝色、深青色、橙色、橙色、浅灰色、灰色、浅黄色、深色调、灰色系</t>
+          <t>近黑色、灰色、蓝色、深暗青色、橙色、亮橙色、浅灰色、浅灰色、浅米黄色</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -4032,8 +4062,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>7124</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>7124</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -4102,7 +4134,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>白色、灰色、深灰色、深灰色、灰色、灰色、灰色、黑色、浅灰色</t>
+          <t>白色、灰色、近黑色、灰色、灰色、灰色、灰色、近黑色、浅灰色</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -4117,7 +4149,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>白色、灰色、深灰色、深灰色、灰色、灰色、灰色、黑色、浅灰色、低饱和色调、灰色系</t>
+          <t>白色、灰色、近黑色、灰色、灰色、灰色、灰色、近黑色、浅灰色</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -4257,8 +4289,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>8624</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>8624</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -4327,7 +4361,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>灰红色、深灰色、灰色、灰色、深灰色、蓝色、灰色、灰蓝色、蓝色</t>
+          <t>灰色、深灰色、灰色、灰色、灰色、蓝色、浅灰色、钴蓝色、蓝色</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -4337,12 +4371,12 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>蓝色系</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>灰红色、深灰色、灰色、灰色、深灰色、蓝色、灰色、灰蓝色、蓝色、低饱和色调、灰色系</t>
+          <t>灰色、深灰色、灰色、灰色、灰色、蓝色、浅灰色、钴蓝色、蓝色</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -4482,8 +4516,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>8633</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8633</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -4552,22 +4588,22 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>白色、白色、白色、深橙色、深橙色、黑色、灰橙色、灰色、浅灰色</t>
+          <t>白色、白色、白色、深灰棕色、深灰棕色、深棕色、灰色、灰色、浅灰色</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>浅色调</t>
+          <t>高明度色调</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>白色、白色、白色、深橙色、深橙色、黑色、灰橙色、灰色、浅灰色、浅色调、灰色系</t>
+          <t>白色、白色、白色、深灰棕色、深灰棕色、深棕色、灰色、灰色、浅灰色</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -4707,8 +4743,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>8958</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8958</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -4777,7 +4815,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>黑色、黑色、黑色、深橙色、深橙色、深橙色、深橙色、深橙色、深橙色</t>
+          <t>深棕色、深棕色、近黑色、深棕色、深棕色、深棕色、深棕色、深棕色、深棕色</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -4787,12 +4825,12 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>黑色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>黑色、黑色、黑色、深橙色、深橙色、深橙色、深橙色、深橙色、深橙色、深色调、黑色系</t>
+          <t>深棕色、深棕色、近黑色、深棕色、深棕色、深棕色、深棕色、深棕色、深棕色</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -4932,8 +4970,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>8991</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>8991</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -5002,7 +5042,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>橙色、橙色、灰青色、灰色、橙色、橙色、蓝色、红色、深蓝色</t>
+          <t>亮橙色、亮橙色、灰青色、浅灰色、橙色、柠檬黄、蓝色、鲜红色、深藏蓝色</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -5017,7 +5057,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>橙色、橙色、灰青色、灰色、橙色、橙色、蓝色、红色、深蓝色、中明度色调、橙色系</t>
+          <t>亮橙色、亮橙色、灰青色、浅灰色、橙色、柠檬黄、蓝色、鲜红色、深藏蓝色</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -5157,8 +5197,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>9010</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>9010</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -5227,7 +5269,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>深绿色、深青色、灰绿色、蓝色、浅青色、白色、蓝色、橙色、灰橙色</t>
+          <t>深灰青色、深灰青色、灰青色、青绿色、浅青色、白色、浅天蓝色、金黄色、浅灰色</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -5237,12 +5279,12 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>绿色系</t>
+          <t>蓝绿色系</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>深绿色、深青色、灰绿色、蓝色、浅青色、白色、蓝色、橙色、灰橙色、中明度色调、绿色系</t>
+          <t>深灰青色、深灰青色、灰青色、青绿色、浅青色、白色、浅天蓝色、金黄色、浅灰色</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -5382,8 +5424,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>9503</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9503</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -5452,7 +5496,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、灰色、白色、浅橙色、灰色、灰色、橙色、橙色</t>
+          <t>深灰棕色、深棕色、灰色、白色、浅灰色、灰色、灰色、亮橙色、橙色</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -5462,12 +5506,12 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、灰色、白色、浅橙色、灰色、灰色、橙色、橙色、低饱和色调、橙色系</t>
+          <t>深灰棕色、深棕色、灰色、白色、浅灰色、灰色、灰色、亮橙色、橙色</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -5607,8 +5651,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>9512</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9512</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -5677,22 +5723,22 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>黑色、黑色、深灰色、深橙色、橙色、浅橙色、橙色、橙色、浅灰色</t>
+          <t>近黑色、近黑色、灰色、深灰棕色、浅柠檬黄、浅米黄色、金黄色、黄色、浅灰色</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>低饱和色调</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>黑色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>黑色、黑色、深灰色、深橙色、橙色、浅橙色、橙色、橙色、浅灰色、深色调、黑色系</t>
+          <t>近黑色、近黑色、灰色、深灰棕色、浅柠檬黄、浅米黄色、金黄色、黄色、浅灰色</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -5832,8 +5878,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>11272</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>11272</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -5902,7 +5950,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>橙色、橙色、橙色、灰色、橙色、浅灰色、灰色、浅橙色、深橙色</t>
+          <t>柠檬黄、金黄色、橙色、灰色、深黄色、浅灰色、灰色、柠檬黄、深棕色</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -5912,12 +5960,12 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>橙色、橙色、橙色、灰色、橙色、浅灰色、灰色、浅橙色、深橙色、中明度色调、橙色系</t>
+          <t>柠檬黄、金黄色、橙色、灰色、深黄色、浅灰色、灰色、柠檬黄、深棕色</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -6057,8 +6105,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>11320</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>11320</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -6127,7 +6177,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>浅灰色、浅灰色、浅灰色、深灰色、深灰色、灰色、黑色、灰色、灰色</t>
+          <t>浅灰色、浅灰色、浅灰色、灰色、灰色、灰色、近黑色、灰色、灰色</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -6142,7 +6192,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>浅灰色、浅灰色、浅灰色、深灰色、深灰色、灰色、黑色、灰色、灰色、低饱和色调、灰色系</t>
+          <t>浅灰色、浅灰色、浅灰色、灰色、灰色、灰色、近黑色、灰色、灰色</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -6282,8 +6332,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>11393</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>11393</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -6352,22 +6404,22 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>深黄色、深黄色、深黄色、深黄色、深橙色、橙色、深橙色、橙色、黄色</t>
+          <t>深棕色、深棕色、深棕色、深棕色、深棕色、橙色、深棕色、橙色、黄色</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>黄色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>深黄色、深黄色、深黄色、深黄色、深橙色、橙色、深橙色、橙色、黄色、深色调、黄色系</t>
+          <t>深棕色、深棕色、深棕色、深棕色、深棕色、橙色、深棕色、橙色、黄色</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -6507,8 +6559,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>11434</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>11434</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -6577,22 +6631,22 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、深橙色、橙色、深橙色、深橙色、橙色、橙色、橙色</t>
+          <t>深棕色、深棕色、深棕色、棕色、深棕色、深暗橙色、橙色、橙色、金黄色</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、深橙色、橙色、深橙色、深橙色、橙色、橙色、橙色、深色调、橙色系</t>
+          <t>深棕色、深棕色、深棕色、棕色、深棕色、深暗橙色、橙色、橙色、金黄色</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -6732,8 +6786,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>11723</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>11723</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -6802,7 +6858,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>灰色、灰色、灰色、灰色、灰橙色、橙色、深黄色、橙色、浅灰色</t>
+          <t>灰色、灰色、浅灰色、灰色、灰色、棕色、深棕色、亮橙色、浅灰色</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -6812,12 +6868,12 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>橙色系</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>灰色、灰色、灰色、灰色、灰橙色、橙色、深黄色、橙色、浅灰色、低饱和色调、灰色系</t>
+          <t>灰色、灰色、浅灰色、灰色、灰色、棕色、深棕色、亮橙色、浅灰色</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -6957,8 +7013,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>13720</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>13720</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -7027,7 +7085,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>灰色、灰色、灰色、灰黄色、灰黄色、浅灰色、深黄色、黑色、深黄色</t>
+          <t>灰色、灰色、灰色、灰色、深灰棕色、浅灰色、深灰棕色、黑色、深棕色</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -7037,12 +7095,12 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>灰色、灰色、灰色、灰黄色、灰黄色、浅灰色、深黄色、黑色、深黄色、低饱和色调、灰色系</t>
+          <t>灰色、灰色、灰色、灰色、深灰棕色、浅灰色、深灰棕色、黑色、深棕色</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -7182,8 +7240,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>13853</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13853</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -7252,7 +7312,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>白色、灰色、浅灰色、灰黄色、灰黄色、浅灰色、黄色、深黄色、深黄色</t>
+          <t>白色、灰色、浅灰色、灰色、灰色、浅灰色、黄色、深棕色、深棕色</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -7262,12 +7322,12 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>白色、灰色、浅灰色、灰黄色、灰黄色、浅灰色、黄色、深黄色、深黄色、低饱和色调、灰色系</t>
+          <t>白色、灰色、浅灰色、灰色、灰色、浅灰色、黄色、深棕色、深棕色</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -7407,8 +7467,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>14572</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14572</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -7477,12 +7539,12 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>橙色、橙色、深绿色、深橙色、黄色、橙色、绿色、橙色、橙色</t>
+          <t>暗橙色、橙色、深灰绿色、深棕色、黄色、亮橙色、绿色、亮橙色、浅柠檬黄</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -7492,7 +7554,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>橙色、橙色、深绿色、深橙色、黄色、橙色、绿色、橙色、橙色、中明度色调、橙色系</t>
+          <t>暗橙色、橙色、深灰绿色、深棕色、黄色、亮橙色、绿色、亮橙色、浅柠檬黄</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -7632,8 +7694,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>14574</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>14574</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -7702,22 +7766,22 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>深橙色、黑色、深橙色、橙色、橙色、橙色、橙色、浅黄色、灰黄色</t>
+          <t>深棕色、黑色、深棕色、暗橙色、黄色、金黄色、浅柠檬黄、浅米黄色、金黄色</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>深橙色、黑色、深橙色、橙色、橙色、橙色、橙色、浅黄色、灰黄色、中明度色调、橙色系</t>
+          <t>深棕色、黑色、深棕色、暗橙色、黄色、金黄色、浅柠檬黄、浅米黄色、金黄色</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -7857,8 +7921,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>14591</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>14591</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -7927,7 +7993,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>深灰色、黑色、灰色、灰色、深灰色、橙色、绿色、浅灰色、橙色</t>
+          <t>近黑色、近黑色、灰色、灰色、灰色、黄色、青色、浅灰色、金黄色</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -7937,12 +8003,12 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>深灰色、黑色、灰色、灰色、深灰色、橙色、绿色、浅灰色、橙色、低饱和色调、灰色系</t>
+          <t>近黑色、近黑色、灰色、灰色、灰色、黄色、青色、浅灰色、金黄色</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -8082,8 +8148,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>14598</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14598</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -8152,7 +8220,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>灰色、灰色、灰青色、灰色、浅灰色、灰橙色、灰色、深灰色、蓝色</t>
+          <t>灰色、灰色、灰青色、灰色、浅灰色、深灰棕色、灰色、深灰色、蓝色</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -8162,12 +8230,12 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>蓝绿色系</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>灰色、灰色、灰青色、灰色、浅灰色、灰橙色、灰色、深灰色、蓝色、低饱和色调、灰色系</t>
+          <t>灰色、灰色、灰青色、灰色、浅灰色、深灰棕色、灰色、深灰色、蓝色</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -8307,8 +8375,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>14655</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14655</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -8377,7 +8447,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>灰色、灰色、灰色、灰黄色、黄色、深蓝色、浅灰色、蓝色、红色</t>
+          <t>灰色、灰色、灰色、深灰棕色、黄色、深藏蓝色、浅灰色、暗青色、鲜红色</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -8387,12 +8457,12 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>灰色、灰色、灰色、灰黄色、黄色、深蓝色、浅灰色、蓝色、红色、低饱和色调、灰色系</t>
+          <t>灰色、灰色、灰色、深灰棕色、黄色、深藏蓝色、浅灰色、暗青色、鲜红色</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -8532,8 +8602,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>14968</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>14968</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -8602,7 +8674,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>红色、红色、红色、红色、红色、浅灰色、红色、深橙色、灰橙色</t>
+          <t>红色、红色、鲜红色、鲜红色、浅玫瑰红、浅灰色、浅橙红色、深灰棕色、灰色</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -8617,7 +8689,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>红色、红色、红色、红色、红色、浅灰色、红色、深橙色、灰橙色、中明度色调、红色系</t>
+          <t>红色、红色、鲜红色、鲜红色、浅玫瑰红、浅灰色、浅橙红色、深灰棕色、灰色</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -8757,8 +8829,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>15401</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>15401</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -8827,7 +8901,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>深灰色、灰色、深灰色、灰橙色、灰橙色、浅灰色、青色、灰青色、浅灰色</t>
+          <t>近黑色、灰色、灰色、灰色、金黄色、浅灰色、青色、蓝绿色、浅灰色</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -8837,12 +8911,12 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>深灰色、灰色、深灰色、灰橙色、灰橙色、浅灰色、青色、灰青色、浅灰色、低饱和色调、灰色系</t>
+          <t>近黑色、灰色、灰色、灰色、金黄色、浅灰色、青色、蓝绿色、浅灰色</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -8982,8 +9056,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>15468</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>15468</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -9052,7 +9128,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>橙色、橙色、浅橙色、深橙色、深橙色、橙色、橙色、灰橙色、黄色</t>
+          <t>亮橙色、浅橙红色、浅橙红色、深棕色、深黄色、亮橙色、橙色、灰色、棕色</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -9067,7 +9143,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>橙色、橙色、浅橙色、深橙色、深橙色、橙色、橙色、灰橙色、黄色、中明度色调、橙色系</t>
+          <t>亮橙色、浅橙红色、浅橙红色、深棕色、深黄色、亮橙色、橙色、灰色、棕色</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -9207,8 +9283,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>15563</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>15563</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -9277,12 +9355,12 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>深蓝色、深红色、深蓝色、深灰色、深红色、灰色、蓝色、灰色、灰橙色</t>
+          <t>深蓝色、深灰棕色、深藏蓝色、近黑色、深棕色、灰色、藏蓝色、灰色、浅灰色</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -9292,7 +9370,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>深蓝色、深红色、深蓝色、深灰色、深红色、灰色、蓝色、灰色、灰橙色、深色调、蓝色系</t>
+          <t>深蓝色、深灰棕色、深藏蓝色、近黑色、深棕色、灰色、藏蓝色、灰色、浅灰色</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -9432,8 +9510,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>16146</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>16146</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -9502,7 +9582,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>浅灰色、灰橙色、灰色、灰色、灰色、灰色、深灰色、红色、橙色</t>
+          <t>浅灰色、浅灰色、浅灰色、灰色、灰色、灰色、灰色、红色、亮橙色</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -9512,12 +9592,12 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>浅灰色、灰橙色、灰色、灰色、灰色、灰色、深灰色、红色、橙色、低饱和色调、灰色系</t>
+          <t>浅灰色、浅灰色、浅灰色、灰色、灰色、灰色、灰色、红色、亮橙色</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -9657,8 +9737,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>16169</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>16169</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -9727,22 +9809,22 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>灰橙色、灰橙色、灰黄色、深黄色、深橙色、灰黄色、橙色、橙色、灰蓝色</t>
+          <t>浅灰色、灰色、黄色、深灰棕色、深棕色、灰色、橙色、亮橙色、钴蓝色</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>低饱和色调</t>
+          <t>中明度色调</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>灰橙色、灰橙色、灰黄色、深黄色、深橙色、灰黄色、橙色、橙色、灰蓝色、低饱和色调、橙色系</t>
+          <t>浅灰色、灰色、黄色、深灰棕色、深棕色、灰色、橙色、亮橙色、钴蓝色</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -9882,8 +9964,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>16231</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>16231</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -9952,12 +10036,12 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>黑色、橙色、深橙色、橙色、橙色、橙色、红色、浅橙色、橙色</t>
+          <t>黑色、亮橙色、深暗橙色、浅柠檬黄、亮橙色、黄色、鲜红色、浅米黄色、金黄色</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
@@ -9967,7 +10051,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>黑色、橙色、深橙色、橙色、橙色、橙色、红色、浅橙色、橙色、深色调、橙色系</t>
+          <t>黑色、亮橙色、深暗橙色、浅柠檬黄、亮橙色、黄色、鲜红色、浅米黄色、金黄色</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -10107,8 +10191,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>16298</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>16298</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -10177,7 +10263,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>黑色、黑色、黑色、黑色、橙色、橙色、橙色、深橙色、橙色</t>
+          <t>黑色、黑色、近黑色、近黑色、橙色、橙色、暗橙色、深棕色、亮橙色</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -10187,12 +10273,12 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>黑色系</t>
+          <t>橙色系</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>黑色、黑色、黑色、黑色、橙色、橙色、橙色、深橙色、橙色、深色调、黑色系</t>
+          <t>黑色、黑色、近黑色、近黑色、橙色、橙色、暗橙色、深棕色、亮橙色</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -10332,8 +10418,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>16327</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>16327</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -10402,22 +10490,22 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、红色、黄色、橙色、灰黄色、深蓝色、深绿色、浅灰色</t>
+          <t>深棕色、深棕色、橙色、深黄色、金黄色、灰绿色、深藏蓝色、深绿色、浅灰色</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、红色、黄色、橙色、灰黄色、深蓝色、深绿色、浅灰色、中明度色调、橙色系</t>
+          <t>深棕色、深棕色、橙色、深黄色、金黄色、灰绿色、深藏蓝色、深绿色、浅灰色</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -10557,8 +10645,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>16362</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>16362</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -10627,12 +10717,12 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>深橙色、橙色、橙色、黑色、橙色、深橙色、橙色、橙色、橙色</t>
+          <t>深暗橙色、暗橙色、金黄色、深棕色、橙色、深棕色、黄色、金黄色、黄色</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
@@ -10642,7 +10732,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>深橙色、橙色、橙色、黑色、橙色、深橙色、橙色、橙色、橙色、中明度色调、橙色系</t>
+          <t>深暗橙色、暗橙色、金黄色、深棕色、橙色、深棕色、黄色、金黄色、黄色</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -10782,8 +10872,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>16487</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>16487</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -10852,7 +10944,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>灰青色、蓝色、蓝色、灰色、灰绿色、橙色、灰色、灰绿色、橙色</t>
+          <t>蓝绿色、蓝色、蓝色、灰色、灰绿色、亮橙色、灰色、暗青色、浅橙红色</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -10867,7 +10959,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>灰青色、蓝色、蓝色、灰色、灰绿色、橙色、灰色、灰绿色、橙色、中明度色调、蓝色系</t>
+          <t>蓝绿色、蓝色、蓝色、灰色、灰绿色、亮橙色、灰色、暗青色、浅橙红色</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -11007,8 +11099,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>16488</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>16488</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -11077,7 +11171,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>灰青色、深橙色、浅橙色、橙色、橙色、灰橙色、深橙色、浅橙色、红色</t>
+          <t>浅灰青色、深棕色、浅橙红色、橙色、亮橙色、亮橙色、深棕色、浅橙色、鲜红色</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -11092,7 +11186,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>灰青色、深橙色、浅橙色、橙色、橙色、灰橙色、深橙色、浅橙色、红色、中明度色调、橙色系</t>
+          <t>浅灰青色、深棕色、浅橙红色、橙色、亮橙色、亮橙色、深棕色、浅橙色、鲜红色</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -11142,7 +11236,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>26.31%</t>
+          <t>26.30%</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -11232,8 +11326,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>16499</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>16499</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -11302,22 +11398,22 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>黑色、深橙色、黑色、深橙色、浅橙色、橙色、橙色、橙色、浅黄色</t>
+          <t>黑色、深棕色、深棕色、深棕色、浅橙红色、亮橙色、橙色、亮橙色、浅灰色</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>黑色、深橙色、黑色、深橙色、浅橙色、橙色、橙色、橙色、浅黄色、深色调、橙色系</t>
+          <t>黑色、深棕色、深棕色、深棕色、浅橙红色、亮橙色、橙色、亮橙色、浅灰色</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -11457,8 +11553,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>16551</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>16551</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -11527,12 +11625,12 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>深橙色、橙色、浅灰色、深橙色、橙色、橙色、橙色、浅橙色、灰色</t>
+          <t>深棕色、浅柠檬黄、浅灰色、深暗橙色、橙色、金黄色、橙色、浅米黄色、灰色</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>高饱和色调</t>
+          <t>中明度色调</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
@@ -11542,7 +11640,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>深橙色、橙色、浅灰色、深橙色、橙色、橙色、橙色、浅橙色、灰色、高饱和色调、橙色系</t>
+          <t>深棕色、浅柠檬黄、浅灰色、深暗橙色、橙色、金黄色、橙色、浅米黄色、灰色</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -11682,8 +11780,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>16568</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>16568</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -11752,7 +11852,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>灰蓝色、蓝色、蓝色、蓝色、灰蓝色、绿色、深青色、灰青色、灰色</t>
+          <t>蓝色、钴蓝色、青色、钴蓝色、青色、绿色、深暗青色、灰青色、灰色</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -11767,7 +11867,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>灰蓝色、蓝色、蓝色、蓝色、灰蓝色、绿色、深青色、灰青色、灰色、中明度色调、蓝色系</t>
+          <t>蓝色、钴蓝色、青色、钴蓝色、青色、绿色、深暗青色、灰青色、灰色</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -11907,8 +12007,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>16571</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>16571</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -11977,7 +12079,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>灰青色、深青色、灰色、灰色、灰色、灰色、深蓝色、灰蓝色、浅灰色</t>
+          <t>暗青色、深暗青色、灰色、灰色、灰色、灰色、深青色、蓝色、浅灰色</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -11987,12 +12089,12 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>蓝绿色系</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>灰青色、深青色、灰色、灰色、灰色、灰色、深蓝色、灰蓝色、浅灰色、低饱和色调、灰色系</t>
+          <t>暗青色、深暗青色、灰色、灰色、灰色、灰色、深青色、蓝色、浅灰色</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -12132,8 +12234,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>16776</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>16776</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -12202,7 +12306,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>浅灰色、灰色、蓝色、灰青色、深灰色、灰青色、白色、浅灰色、橙色</t>
+          <t>浅灰色、灰色、暗青色、青色、灰色、浅青绿色、白色、浅灰色、橙色</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -12212,12 +12316,12 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>蓝绿色系</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>浅灰色、灰色、蓝色、灰青色、深灰色、灰青色、白色、浅灰色、橙色、低饱和色调、灰色系</t>
+          <t>浅灰色、灰色、暗青色、青色、灰色、浅青绿色、白色、浅灰色、橙色</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -12357,8 +12461,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>16964</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>16964</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -12427,7 +12533,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>浅黄色、灰黄色、青色、橙色、灰青色、蓝色、浅灰色、橙色、深红色</t>
+          <t>浅柠檬黄、浅灰色、青色、亮橙色、蓝绿色、钴蓝色、浅灰色、亮橙色、深灰棕色</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -12437,12 +12543,12 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>黄色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>浅黄色、灰黄色、青色、橙色、灰青色、蓝色、浅灰色、橙色、深红色、中明度色调、黄色系</t>
+          <t>浅柠檬黄、浅灰色、青色、亮橙色、蓝绿色、钴蓝色、浅灰色、亮橙色、深灰棕色</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -12582,8 +12688,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>18709</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>18709</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -12652,7 +12760,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>浅橙色、深青色、深青色、灰色、灰青色、灰色、浅灰色、灰色、灰绿色</t>
+          <t>浅灰色、深暗青色、深灰青色、灰色、灰青色、灰色、浅灰色、灰色、灰青色</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -12662,12 +12770,12 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>蓝绿色系</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>浅橙色、深青色、深青色、灰色、灰青色、灰色、浅灰色、灰色、灰绿色、低饱和色调、橙色系</t>
+          <t>浅灰色、深暗青色、深灰青色、灰色、灰青色、灰色、浅灰色、灰色、灰青色</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -12807,8 +12915,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>18757</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>18757</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -12877,7 +12987,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>深灰色、深灰色、橙色、灰色、橙色、浅橙色、橙色、浅橙色、青色</t>
+          <t>灰色、灰色、浅柠檬黄、灰色、金黄色、浅柠檬黄、黄色、浅米黄色、蓝绿色</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -12887,12 +12997,12 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>深灰色、深灰色、橙色、灰色、橙色、浅橙色、橙色、浅橙色、青色、低饱和色调、灰色系</t>
+          <t>灰色、灰色、浅柠檬黄、灰色、金黄色、浅柠檬黄、黄色、浅米黄色、蓝绿色</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -13032,8 +13142,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>19339</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>19339</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -13102,7 +13214,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>绿色、灰橙色、橙色、深蓝色、黄色、黄色、绿色、红色、灰蓝色</t>
+          <t>深绿色、浅柠檬黄、金黄色、深蓝色、黄色、金黄色、绿色、鲜红色、灰青色</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -13112,12 +13224,12 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>绿色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>绿色、灰橙色、橙色、深蓝色、黄色、黄色、绿色、红色、灰蓝色、中明度色调、绿色系</t>
+          <t>深绿色、浅柠檬黄、金黄色、深蓝色、黄色、金黄色、绿色、鲜红色、灰青色</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -13257,8 +13369,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>20432</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20432</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -13327,12 +13441,12 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>浅橙色、浅橙色、浅橙色、橙色、红色、橙色、灰橙色、灰色、红色</t>
+          <t>浅橙红色、浅橙红色、浅橙红色、浅橙红色、亮橙色、亮橙色、亮橙色、灰色、橙色</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>浅色调</t>
+          <t>中明度色调</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
@@ -13342,7 +13456,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>浅橙色、浅橙色、浅橙色、橙色、红色、橙色、灰橙色、灰色、红色、浅色调、橙色系</t>
+          <t>浅橙红色、浅橙红色、浅橙红色、浅橙红色、亮橙色、亮橙色、亮橙色、灰色、橙色</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -13482,8 +13596,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>20579</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20579</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -13552,22 +13668,22 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>黑色、深橙色、深橙色、深橙色、橙色、橙色、橙色、橙色、橙色</t>
+          <t>深棕色、深棕色、深棕色、深棕色、棕色、黄色、黄色、金黄色、金黄色</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>黑色、深橙色、深橙色、深橙色、橙色、橙色、橙色、橙色、橙色、深色调、橙色系</t>
+          <t>深棕色、深棕色、深棕色、深棕色、棕色、黄色、黄色、金黄色、金黄色</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -13707,8 +13823,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>20684</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20684</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -13777,7 +13895,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>灰色、灰色、浅灰色、灰色、黑色、深蓝色、深蓝色、灰色、红色</t>
+          <t>灰色、浅灰色、浅灰色、灰色、深藏蓝色、深蓝色、深蓝灰色、灰色、橙色</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -13787,12 +13905,12 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>蓝色系</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>灰色、灰色、浅灰色、灰色、黑色、深蓝色、深蓝色、灰色、红色、低饱和色调、灰色系</t>
+          <t>灰色、浅灰色、浅灰色、灰色、深藏蓝色、深蓝色、深蓝灰色、灰色、橙色</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -13932,8 +14050,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>21023</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>21023</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -14002,7 +14122,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>深灰色、灰色、灰色、灰橙色、深橙色、浅灰色、灰橙色、深橙色、灰色</t>
+          <t>灰色、灰色、灰色、橙色、深棕色、浅灰色、灰色、深棕色、浅灰色</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -14012,12 +14132,12 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>橙色系</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>深灰色、灰色、灰色、灰橙色、深橙色、浅灰色、灰橙色、深橙色、灰色、低饱和色调、灰色系</t>
+          <t>灰色、灰色、灰色、橙色、深棕色、浅灰色、灰色、深棕色、浅灰色</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -14157,8 +14277,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>23333</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>23333</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -14227,22 +14349,22 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>黑色、深橙色、深橙色、橙色、橙色、橙色、橙色、浅橙色、浅橙色</t>
+          <t>深棕色、深棕色、深暗橙色、暗橙色、橙色、亮橙色、亮橙色、浅橙色、浅橙红色</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>黑色、深橙色、深橙色、橙色、橙色、橙色、橙色、浅橙色、浅橙色、深色调、橙色系</t>
+          <t>深棕色、深棕色、深暗橙色、暗橙色、橙色、亮橙色、亮橙色、浅橙色、浅橙红色</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
@@ -14382,8 +14504,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>23506</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>23506</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -14452,22 +14576,22 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>浅灰色、浅灰色、浅灰色、浅橙色、浅灰色、灰橙色、灰橙色、灰橙色、深橙色</t>
+          <t>浅灰色、浅灰色、浅灰色、浅灰色、浅灰色、灰色、灰色、灰色、深灰棕色</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>浅色调</t>
+          <t>高明度色调</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>浅灰色、浅灰色、浅灰色、浅橙色、浅灰色、灰橙色、灰橙色、灰橙色、深橙色、浅色调、灰色系</t>
+          <t>浅灰色、浅灰色、浅灰色、浅灰色、浅灰色、灰色、灰色、灰色、深灰棕色</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
@@ -14607,8 +14731,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>23684</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>23684</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -14677,7 +14803,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>橙色、橙色、橙色、橙色、橙色、灰橙色、橙色、浅橙色、浅橙色</t>
+          <t>橙色、橙色、亮橙色、橙色、亮橙色、棕色、亮橙色、浅灰色、浅橙色</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -14692,7 +14818,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>橙色、橙色、橙色、橙色、橙色、灰橙色、橙色、浅橙色、浅橙色、中明度色调、橙色系</t>
+          <t>橙色、橙色、亮橙色、橙色、亮橙色、棕色、亮橙色、浅灰色、浅橙色</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -14832,8 +14958,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>23700</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>23700</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -14902,7 +15030,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>黑色、浅灰色、深橙色、浅灰色、灰色、灰橙色、灰黄色、灰橙色、深橙色</t>
+          <t>近黑色、浅灰色、深灰棕色、浅灰色、灰色、灰色、灰色、灰色、深棕色</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -14912,12 +15040,12 @@
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>黑色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>黑色、浅灰色、深橙色、浅灰色、灰色、灰橙色、灰黄色、灰橙色、深橙色、低饱和色调、黑色系</t>
+          <t>近黑色、浅灰色、深灰棕色、浅灰色、灰色、灰色、灰色、灰色、深棕色</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
@@ -15057,8 +15185,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>23972</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>23972</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -15127,22 +15257,22 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>黑色、深橙色、深红色、橙色、浅灰色、灰青色、橙色、青色、红色</t>
+          <t>深墨绿色、深黄色、深棕色、黄色、浅灰色、蓝绿色、亮橙色、青色、鲜红色</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>绿色系</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>黑色、深橙色、深红色、橙色、浅灰色、灰青色、橙色、青色、红色、中明度色调、橙色系</t>
+          <t>深墨绿色、深黄色、深棕色、黄色、浅灰色、蓝绿色、亮橙色、青色、鲜红色</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
@@ -15282,8 +15412,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>24306</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>24306</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -15352,22 +15484,22 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>深蓝色、深青色、浅灰色、绿色、灰绿色、青色、绿色、灰青色、蓝色</t>
+          <t>深蓝色、深暗青色、浅灰色、青色、草绿色、蓝绿色、绿色、蓝绿色、蓝色</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>青色系</t>
+          <t>蓝绿色系</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>深蓝色、深青色、浅灰色、绿色、灰绿色、青色、绿色、灰青色、蓝色、中明度色调、青色系</t>
+          <t>深蓝色、深暗青色、浅灰色、青色、草绿色、蓝绿色、绿色、蓝绿色、蓝色</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -15507,8 +15639,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>24548</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>24548</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -15577,7 +15711,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>灰色、浅灰色、灰色、灰色、黄色、深黄色、浅灰色、黄色、深黄色</t>
+          <t>灰色、浅灰色、灰色、灰色、黄色、深棕色、浅灰色、金黄色、深棕色</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -15587,12 +15721,12 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>灰色、浅灰色、灰色、灰色、黄色、深黄色、浅灰色、黄色、深黄色、低饱和色调、灰色系</t>
+          <t>灰色、浅灰色、灰色、灰色、黄色、深棕色、浅灰色、金黄色、深棕色</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -15732,8 +15866,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>24836</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>24836</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -15802,7 +15938,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>灰红色、灰红色、红色、深橙色、红色、浅黄色、蓝色、橙色、黄色</t>
+          <t>浅橙红色、浅橙红色、亮橙色、深棕色、鲜红色、米黄色、蓝色、棕色、金黄色</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -15812,12 +15948,12 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>红色系</t>
+          <t>橙色系</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>灰红色、灰红色、红色、深橙色、红色、浅黄色、蓝色、橙色、黄色、中明度色调、红色系</t>
+          <t>浅橙红色、浅橙红色、亮橙色、深棕色、鲜红色、米黄色、蓝色、棕色、金黄色</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -15957,8 +16093,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>25332</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>25332</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -16027,22 +16165,22 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>黑色、灰黄色、浅灰色、灰色、深黄色、黄色、深黄色、黄色、浅灰色</t>
+          <t>黑色、浅灰色、浅灰色、灰色、深棕色、金黄色、深棕色、黄色、浅灰色</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>低饱和色调</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>黑色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>黑色、灰黄色、浅灰色、灰色、深黄色、黄色、深黄色、黄色、浅灰色、深色调、黑色系</t>
+          <t>黑色、浅灰色、浅灰色、灰色、深棕色、金黄色、深棕色、黄色、浅灰色</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -16182,8 +16320,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>25853</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>25853</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -16252,22 +16392,22 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>灰色、灰色、浅灰色、黄色、灰色、橙色、浅黄色、深黄色、浅橙色</t>
+          <t>灰色、灰色、浅灰色、金黄色、灰色、金黄色、浅柠檬黄、深黄色、米黄色</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>低饱和色调</t>
+          <t>中明度色调</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>灰色、灰色、浅灰色、黄色、灰色、橙色、浅黄色、深黄色、浅橙色、低饱和色调、灰色系</t>
+          <t>灰色、灰色、浅灰色、金黄色、灰色、金黄色、浅柠檬黄、深黄色、米黄色</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
@@ -16407,8 +16547,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>25865</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>25865</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -16477,12 +16619,12 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>橙色、橙色、深橙色、深黄色、深绿色、深橙色、灰黄色、灰黄色、灰黄色</t>
+          <t>橙色、橙色、深棕色、深棕色、深灰绿色、深棕色、深灰色、灰色、灰色</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
@@ -16492,7 +16634,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>橙色、橙色、深橙色、深黄色、深绿色、深橙色、灰黄色、灰黄色、灰黄色、中明度色调、橙色系</t>
+          <t>橙色、橙色、深棕色、深棕色、深灰绿色、深棕色、深灰色、灰色、灰色</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -16632,8 +16774,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>27307</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>27307</t>
+        </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -16702,7 +16846,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>灰橙色、橙色、浅灰色、灰橙色、橙色、灰橙色、橙色、深橙色、橙色</t>
+          <t>亮橙色、亮橙色、浅灰色、浅灰色、橙色、亮橙色、橙色、深暗橙色、亮橙色</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -16717,7 +16861,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>灰橙色、橙色、浅灰色、灰橙色、橙色、灰橙色、橙色、深橙色、橙色、中明度色调、橙色系</t>
+          <t>亮橙色、亮橙色、浅灰色、浅灰色、橙色、亮橙色、橙色、深暗橙色、亮橙色</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -16857,8 +17001,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>27310</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>27310</t>
+        </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -16927,12 +17073,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>深橙色、黑色、橙色、红色、深青色、橙色、橙色、浅橙色、红色</t>
+          <t>深棕色、近黑色、橙色、鲜红色、深灰青色、亮橙色、浅橙红色、浅橙色、红色</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>高饱和色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
@@ -16942,7 +17088,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>深橙色、黑色、橙色、红色、深青色、橙色、橙色、浅橙色、红色、高饱和色调、橙色系</t>
+          <t>深棕色、近黑色、橙色、鲜红色、深灰青色、亮橙色、浅橙红色、浅橙色、红色</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
@@ -17082,8 +17228,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>27984</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>27984</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -17152,12 +17300,12 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>橙色、灰蓝色、深橙色、深橙色、橙色、橙色、蓝色、灰青色、灰色</t>
+          <t>橙色、青色、深暗橙色、深棕色、橙色、亮橙色、青色、灰青色、浅灰色</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
@@ -17167,7 +17315,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>橙色、灰蓝色、深橙色、深橙色、橙色、橙色、蓝色、灰青色、灰色、中明度色调、橙色系</t>
+          <t>橙色、青色、深暗橙色、深棕色、橙色、亮橙色、青色、灰青色、浅灰色</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -17307,8 +17455,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>27987</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>27987</t>
+        </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -17377,22 +17527,22 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>深红色、深灰色、深灰色、灰色、深橙色、深灰色、橙色、橙色、灰色</t>
+          <t>深棕色、近黑色、灰色、灰色、深暗橙色、灰色、亮橙色、橙色、灰色</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>深红色、深灰色、深灰色、灰色、深橙色、深灰色、橙色、橙色、灰色、深色调、灰色系</t>
+          <t>深棕色、近黑色、灰色、灰色、深暗橙色、灰色、亮橙色、橙色、灰色</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
@@ -17532,8 +17682,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>27992</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>27992</t>
+        </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -17602,7 +17754,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>灰色、深灰色、灰色、黄色、灰色、灰黄色、橙色、灰色、灰色</t>
+          <t>深灰色、深灰色、灰色、金黄色、灰色、黄色、金黄色、灰色、浅灰色</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -17612,12 +17764,12 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>灰色、深灰色、灰色、黄色、灰色、灰黄色、橙色、灰色、灰色、低饱和色调、灰色系</t>
+          <t>深灰色、深灰色、灰色、金黄色、灰色、黄色、金黄色、灰色、浅灰色</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
@@ -17757,8 +17909,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>28067</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>28067</t>
+        </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -17827,22 +17981,22 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>深青色、深青色、深蓝色、深蓝色、青色、深绿色、青色、深青色、青色</t>
+          <t>深暗青色、深青色、近黑色、深暗青色、暗青色、深灰绿色、青色、深暗青色、青色</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>青色系</t>
+          <t>蓝绿色系</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>深青色、深青色、深蓝色、深蓝色、青色、深绿色、青色、深青色、青色、深色调、青色系</t>
+          <t>深暗青色、深青色、近黑色、深暗青色、暗青色、深灰绿色、青色、深暗青色、青色</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -17982,8 +18136,10 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
-        <v>28560</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>28560</t>
+        </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -18052,7 +18208,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>灰蓝色、灰绿色、灰橙色、橙色、灰橙色、橙色、灰绿色、灰黄色、黄色</t>
+          <t>钴蓝色、灰青色、灰色、金黄色、黄色、亮橙色、深灰绿色、浅柠檬黄、金黄色</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -18062,12 +18218,12 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>灰蓝色、灰绿色、灰橙色、橙色、灰橙色、橙色、灰绿色、灰黄色、黄色、中明度色调、橙色系</t>
+          <t>钴蓝色、灰青色、灰色、金黄色、黄色、亮橙色、深灰绿色、浅柠檬黄、金黄色</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -18207,8 +18363,10 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>28849</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>28849</t>
+        </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -18277,7 +18435,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>浅橙色、浅橙色、浅灰色、绿色、绿色、绿色、深绿色、黄色、深绿色</t>
+          <t>浅柠檬黄、浅柠檬黄、浅灰色、草绿色、绿色、绿色、深绿色、金黄色、深墨绿色</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -18287,12 +18445,12 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>绿色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>浅橙色、浅橙色、浅灰色、绿色、绿色、绿色、深绿色、黄色、深绿色、中明度色调、绿色系</t>
+          <t>浅柠檬黄、浅柠檬黄、浅灰色、草绿色、绿色、绿色、深绿色、金黄色、深墨绿色</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -18432,8 +18590,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
-        <v>30709</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>30709</t>
+        </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -18502,12 +18662,12 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>橙色、橙色、橙色、橙色、橙色、橙色、深橙色、深橙色、橙色</t>
+          <t>橙色、橙色、暗橙色、橙色、亮橙色、亮橙色、深暗橙色、深棕色、浅橙红色</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>高饱和色调</t>
+          <t>中明度色调</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
@@ -18517,7 +18677,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>橙色、橙色、橙色、橙色、橙色、橙色、深橙色、深橙色、橙色、高饱和色调、橙色系</t>
+          <t>橙色、橙色、暗橙色、橙色、亮橙色、亮橙色、深暗橙色、深棕色、浅橙红色</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -18657,8 +18817,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>30839</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>30839</t>
+        </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -18727,22 +18889,22 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、灰黄色、黄色、浅橙色、橙色、绿色、橙色、灰橙色</t>
+          <t>深棕色、深棕色、黄色、深黄色、浅灰色、亮橙色、绿色、橙色、金黄色</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、灰黄色、黄色、浅橙色、橙色、绿色、橙色、灰橙色、中明度色调、橙色系</t>
+          <t>深棕色、深棕色、黄色、深黄色、浅灰色、亮橙色、绿色、橙色、金黄色</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
@@ -18882,8 +19044,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>31285</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>31285</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -18952,7 +19116,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>黑色、深橙色、黑色、深黄色、深橙色、橙色、橙色、浅橙色、橙色</t>
+          <t>深棕色、深棕色、近黑色、深棕色、深棕色、亮橙色、浅橙红色、浅灰色、橙色</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -18962,12 +19126,12 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>黑色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>黑色、深橙色、黑色、深黄色、深橙色、橙色、橙色、浅橙色、橙色、深色调、黑色系</t>
+          <t>深棕色、深棕色、近黑色、深棕色、深棕色、亮橙色、浅橙红色、浅灰色、橙色</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -19107,8 +19271,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>34116</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>34116</t>
+        </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -19177,7 +19343,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>灰色、灰色、浅灰色、黑色、灰色、浅灰色、深灰色、深橙色、灰橙色</t>
+          <t>灰色、灰色、浅灰色、深棕色、灰色、浅灰色、灰色、深灰棕色、灰色</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -19187,12 +19353,12 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>灰色、灰色、浅灰色、黑色、灰色、浅灰色、深灰色、深橙色、灰橙色、低饱和色调、灰色系</t>
+          <t>灰色、灰色、浅灰色、深棕色、灰色、浅灰色、灰色、深灰棕色、灰色</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -19332,8 +19498,10 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>34181</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>34181</t>
+        </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -19402,12 +19570,12 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>橙色、橙色、深橙色、灰橙色、深橙色、深橙色、灰橙色、橙色、灰橙色</t>
+          <t>橙色、橙色、深棕色、深灰色、深灰棕色、深灰棕色、浅灰色、橙色、灰色</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -19417,7 +19585,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>橙色、橙色、深橙色、灰橙色、深橙色、深橙色、灰橙色、橙色、灰橙色、中明度色调、橙色系</t>
+          <t>橙色、橙色、深棕色、深灰色、深灰棕色、深灰棕色、浅灰色、橙色、灰色</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -19557,8 +19725,10 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>34286</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>34286</t>
+        </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -19627,22 +19797,22 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>白色、浅黄色、灰黄色、橙色、橙色、橙色、橙色、橙色、红色</t>
+          <t>白色、浅灰色、浅灰色、金黄色、金黄色、金黄色、橙色、浅柠檬黄、红色</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>浅色调</t>
+          <t>中明度色调</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>白色、浅黄色、灰黄色、橙色、橙色、橙色、橙色、橙色、红色、浅色调、橙色系</t>
+          <t>白色、浅灰色、浅灰色、金黄色、金黄色、金黄色、橙色、浅柠檬黄、红色</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -19782,8 +19952,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>34299</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>34299</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -19852,7 +20024,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>白色、灰橙色、灰橙色、灰橙色、灰橙色、灰色、浅灰色、深橙色、浅灰色</t>
+          <t>白色、灰色、灰色、灰色、深灰棕色、浅灰色、浅灰色、深灰棕色、浅灰色</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -19862,12 +20034,12 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>橙色系</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>白色、灰橙色、灰橙色、灰橙色、灰橙色、灰色、浅灰色、深橙色、浅灰色、低饱和色调、灰色系</t>
+          <t>白色、灰色、灰色、灰色、深灰棕色、浅灰色、浅灰色、深灰棕色、浅灰色</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -20007,8 +20179,10 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>35198</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>35198</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -20077,22 +20251,22 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>浅黄色、浅黄色、浅粉紫色、灰色、深灰色、紫色、橙色、橙色、浅黄色</t>
+          <t>浅灰色、浅灰色、浅玫瑰粉、灰色、深灰色、蓝色、亮橙色、亮橙色、柠檬黄</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>浅色调</t>
+          <t>低饱和色调</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>黄色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>浅黄色、浅黄色、浅粉紫色、灰色、深灰色、紫色、橙色、橙色、浅黄色、浅色调、黄色系</t>
+          <t>浅灰色、浅灰色、浅玫瑰粉、灰色、深灰色、蓝色、亮橙色、亮橙色、柠檬黄</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -20232,8 +20406,10 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>35376</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>35376</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -20302,7 +20478,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>黑色、深灰色、黑色、橙色、橙色、橙色、灰橙色、深橙色、浅橙色</t>
+          <t>黑色、近黑色、近黑色、亮橙色、橙色、亮橙色、浅橙红色、深棕色、浅灰色</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -20312,12 +20488,12 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>黑色系</t>
+          <t>橙色系</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>黑色、深灰色、黑色、橙色、橙色、橙色、灰橙色、深橙色、浅橙色、深色调、黑色系</t>
+          <t>黑色、近黑色、近黑色、亮橙色、橙色、亮橙色、浅橙红色、深棕色、浅灰色</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -20367,7 +20543,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>53.12%</t>
+          <t>53.13%</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -20457,8 +20633,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
-        <v>36132</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>36132</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -20527,22 +20705,22 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>深灰色、深橙色、橙色、深橙色、橙色、橙色、橙色、黄色、橙色</t>
+          <t>灰色、深暗橙色、橙色、深棕色、金黄色、黄色、金黄色、黄色、浅柠檬黄</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>深灰色、深橙色、橙色、深橙色、橙色、橙色、橙色、黄色、橙色、中明度色调、橙色系</t>
+          <t>灰色、深暗橙色、橙色、深棕色、金黄色、黄色、金黄色、黄色、浅柠檬黄</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
@@ -20682,8 +20860,10 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
-        <v>36161</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>36161</t>
+        </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -20752,7 +20932,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>浅灰色、深红色、深橙色、浅灰色、灰橙色、灰橙色、橙色、红色、灰橙色</t>
+          <t>浅灰色、深棕色、深棕色、浅灰色、浅灰色、黄色、橙色、红色、灰色</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -20762,12 +20942,12 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>浅灰色、深红色、深橙色、浅灰色、灰橙色、灰橙色、橙色、红色、灰橙色、中明度色调、橙色系</t>
+          <t>浅灰色、深棕色、深棕色、浅灰色、浅灰色、黄色、橙色、红色、灰色</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -20907,8 +21087,10 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
-        <v>37368</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>37368</t>
+        </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -20977,22 +21159,22 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>浅灰色、浅灰色、浅灰色、浅灰色、灰黄色、橙色、橙色、灰色、深橙色</t>
+          <t>浅灰色、浅灰色、浅灰色、浅灰色、浅灰色、橙色、金黄色、灰色、深棕色</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>浅色调</t>
+          <t>高明度色调</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>浅灰色、浅灰色、浅灰色、浅灰色、灰黄色、橙色、橙色、灰色、深橙色、浅色调、灰色系</t>
+          <t>浅灰色、浅灰色、浅灰色、浅灰色、浅灰色、橙色、金黄色、灰色、深棕色</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -21132,8 +21314,10 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
-        <v>37761</v>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>37761</t>
+        </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -21202,12 +21386,12 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>白色、浅灰色、浅灰色、深灰色、深灰色、浅灰色、黑色、深灰色、灰色</t>
+          <t>白色、浅灰色、浅灰色、近黑色、灰色、浅灰色、近黑色、灰色、灰色</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>浅色调</t>
+          <t>高明度色调</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
@@ -21217,7 +21401,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>白色、浅灰色、浅灰色、深灰色、深灰色、浅灰色、黑色、深灰色、灰色、浅色调、灰色系</t>
+          <t>白色、浅灰色、浅灰色、近黑色、灰色、浅灰色、近黑色、灰色、灰色</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -21357,8 +21541,10 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
-        <v>38930</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>38930</t>
+        </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -21427,7 +21613,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>红色、红色、灰粉紫色、红色、红色、灰红色、灰红色、红色、浅橙色</t>
+          <t>鲜红色、鲜红色、浅灰色、鲜红色、红色、浅灰红色、鲜红色、红色、浅柠檬黄</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -21442,7 +21628,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>红色、红色、灰粉紫色、红色、红色、灰红色、灰红色、红色、浅橙色、中明度色调、红色系</t>
+          <t>鲜红色、鲜红色、浅灰色、鲜红色、红色、浅灰红色、鲜红色、红色、浅柠檬黄</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -21582,8 +21768,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>40619</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>40619</t>
+        </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -21652,12 +21840,12 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>黑色、深橙色、深橙色、红色、深橙色、橙色、深橙色、橙色、橙色</t>
+          <t>近黑色、深棕色、深暗橙色、暗橙色、深棕色、橙色、深棕色、橙色、亮橙色</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
@@ -21667,7 +21855,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>黑色、深橙色、深橙色、红色、深橙色、橙色、深橙色、橙色、橙色、深色调、橙色系</t>
+          <t>近黑色、深棕色、深暗橙色、暗橙色、深棕色、橙色、深棕色、橙色、亮橙色</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -21807,8 +21995,10 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>42566</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>42566</t>
+        </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -21877,7 +22067,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>灰色、灰色、灰色、浅灰色、白色、灰色、深橙色、橙色、青色</t>
+          <t>灰色、灰色、灰色、浅灰色、白色、灰色、深棕色、亮橙色、暗青色</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -21887,12 +22077,12 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>灰色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>灰色、灰色、灰色、浅灰色、白色、灰色、深橙色、橙色、青色、低饱和色调、灰色系</t>
+          <t>灰色、灰色、灰色、浅灰色、白色、灰色、深棕色、亮橙色、暗青色</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -22032,8 +22222,10 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
-        <v>43060</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>43060</t>
+        </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -22102,7 +22294,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>深灰色、灰色、灰色、灰色、灰色、深灰色、深灰色、浅灰色、浅灰色</t>
+          <t>近黑色、灰色、灰色、灰色、灰色、灰色、灰色、浅灰色、浅灰色</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -22117,7 +22309,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>深灰色、灰色、灰色、灰色、灰色、深灰色、深灰色、浅灰色、浅灰色、低饱和色调、灰色系</t>
+          <t>近黑色、灰色、灰色、灰色、灰色、灰色、灰色、浅灰色、浅灰色</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -22257,8 +22449,10 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
-        <v>43145</v>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>43145</t>
+        </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -22327,22 +22521,22 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>黑色、深黄色、深黄色、浅蓝色、灰蓝色、浅蓝色、黄色、浅灰色、灰色</t>
+          <t>深墨绿色、深棕色、深棕色、浅天蓝色、浅蓝灰色、浅天蓝色、深黄色、浅灰色、灰色</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>黄色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>黑色、深黄色、深黄色、浅蓝色、灰蓝色、浅蓝色、黄色、浅灰色、灰色、中明度色调、黄色系</t>
+          <t>深墨绿色、深棕色、深棕色、浅天蓝色、浅蓝灰色、浅天蓝色、深黄色、浅灰色、灰色</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -22482,8 +22676,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
-        <v>43714</v>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>43714</t>
+        </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -22552,22 +22748,22 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>黄色、黄色、灰黄色、深橙色、深橙色、灰黄色、黑色、橙色、浅灰色</t>
+          <t>黄色、黄色、灰色、深棕色、深棕色、浅灰色、近黑色、金黄色、浅灰色</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>中明度色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>黄色系</t>
+          <t>黄色金色系</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>黄色、黄色、灰黄色、深橙色、深橙色、灰黄色、黑色、橙色、浅灰色、中明度色调、黄色系</t>
+          <t>黄色、黄色、灰色、深棕色、深棕色、浅灰色、近黑色、金黄色、浅灰色</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -22707,8 +22903,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
-        <v>44018</v>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>44018</t>
+        </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -22777,22 +22975,22 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、深橙色、深青色、灰黄色、红色、青色、橙色、灰黄色</t>
+          <t>深棕色、深棕色、深黄色、深暗青色、黄色、红色、青色、黄色、浅灰色</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>深色调</t>
+          <t>中低明度色调</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>橙色系</t>
+          <t>棕色大地色系</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>深橙色、深橙色、深橙色、深青色、灰黄色、红色、青色、橙色、灰黄色、深色调、橙色系</t>
+          <t>深棕色、深棕色、深黄色、深暗青色、黄色、红色、青色、黄色、浅灰色</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
@@ -22932,8 +23130,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
-        <v>44741</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>44741</t>
+        </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -23002,7 +23202,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>白色、橙色、橙色、橙色、白色、深橙色、灰橙色、深橙色、灰橙色</t>
+          <t>白色、橙色、橙色、橙色、白色、深棕色、亮橙色、深棕色、浅灰色</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -23017,7 +23217,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>白色、橙色、橙色、橙色、白色、深橙色、灰橙色、深橙色、灰橙色、低饱和色调、橙色系</t>
+          <t>白色、橙色、橙色、橙色、白色、深棕色、亮橙色、深棕色、浅灰色</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -23155,6 +23355,3658 @@
           <t>灰橙色</t>
         </is>
       </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>900001</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>"Love Story" (Snap Adds 24-sheeter film poster), 1946, by Sam Hood (12491832193) (2)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons / 电影海报资料</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>900001_palette.png</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/900001_palette.png</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>灰色、白色、灰色、灰色、灰色、浅灰色、灰色、灰色、浅灰色</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>低饱和色调</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>灰色系</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>灰色、白色、灰色、灰色、灰色、浅灰色、灰色、灰色、浅灰色</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>#4C4C4C</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>#EAEAEA</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>#878787</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>#737373</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>#616161</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>#D1D1D1</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>#3B3B3B</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>#9D9D9D</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>#B6B6B6</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14.69%</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>12.62%</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>12.41%</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>12.34%</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>11.75%</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>10.77%</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>9.35%</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>9.28%</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>6.78%</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr"/>
+      <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr"/>
+      <c r="AO102" t="inlineStr"/>
+      <c r="AP102" t="inlineStr"/>
+      <c r="AQ102" t="inlineStr"/>
+      <c r="AR102" t="inlineStr"/>
+      <c r="AS102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>900002</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>"Paulchens Millionenkuss"</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons / 电影海报资料</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>900002_palette.png</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/900002_palette.png</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>浅米黄色、深棕色、浅米黄色、浅米黄色、浅柠檬黄、浅柠檬黄、深棕色、金黄色、黄色</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>中明度色调</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>黄色金色系</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>浅米黄色、深棕色、浅米黄色、浅米黄色、浅柠檬黄、浅柠檬黄、深棕色、金黄色、黄色</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>#EBCA85</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>#38382B</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>#F0D495</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>#E4BF73</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>#C6A452</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>#D4B160</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>#504E3A</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>#A78B4A</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>#806F3F</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>29.54%</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>14.34%</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>13.37%</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>11.12%</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>10.61%</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>9.60%</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>5.37%</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>2.94%</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr"/>
+      <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr"/>
+      <c r="AO103" t="inlineStr"/>
+      <c r="AP103" t="inlineStr"/>
+      <c r="AQ103" t="inlineStr"/>
+      <c r="AR103" t="inlineStr"/>
+      <c r="AS103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>900003</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>"Projekt Marmor – verdrängt und vergessen" offizielles Filmposter (deutsch)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons / 电影海报资料</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>900003_palette.png</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/900003_palette.png</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>黑色、深墨绿色、深墨绿色、浅灰色、绿色、灰色、灰色、灰色、草绿色</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>深色调</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>绿色系</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>黑色、深墨绿色、深墨绿色、浅灰色、绿色、灰色、灰色、灰色、草绿色</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>#0A0D09</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>#1B2513</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>#2F3F25</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>#DEDFDE</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>#446C2C</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>#505150</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>#787A77</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>#ACB0A4</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>#73973E</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>46.34%</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>14.28%</t>
+        </is>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t>10.39%</t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>8.88%</t>
+        </is>
+      </c>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>6.11%</t>
+        </is>
+      </c>
+      <c r="AG104" t="inlineStr">
+        <is>
+          <t>4.95%</t>
+        </is>
+      </c>
+      <c r="AH104" t="inlineStr">
+        <is>
+          <t>3.78%</t>
+        </is>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>3.22%</t>
+        </is>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>2.06%</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr"/>
+      <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr"/>
+      <c r="AO104" t="inlineStr"/>
+      <c r="AP104" t="inlineStr"/>
+      <c r="AQ104" t="inlineStr"/>
+      <c r="AR104" t="inlineStr"/>
+      <c r="AS104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>900004</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>"האיש הנעלם - הסיפור של וילפריד ישראל" - פוסטר</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons / 电影海报资料</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>900004_palette.png</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/900004_palette.png</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>浅柠檬黄、浅灰色、浅柠檬黄、灰色、灰色、深灰棕色、深灰色、金黄色、黑色</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>中明度色调</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>黄色金色系</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>浅柠檬黄、浅灰色、浅柠檬黄、灰色、灰色、深灰棕色、深灰色、金黄色、黑色</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>#CDC3A2</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>#DBD3B6</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>#BDB08F</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>#847C6B</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>#9E9685</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>#3D3932</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>#635E53</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>#B29E6D</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>#050504</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>22.75%</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>20.36%</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>18.19%</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>9.55%</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>8.57%</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>7.16%</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>6.10%</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>5.48%</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr"/>
+      <c r="AL105" t="inlineStr"/>
+      <c r="AM105" t="inlineStr"/>
+      <c r="AN105" t="inlineStr"/>
+      <c r="AO105" t="inlineStr"/>
+      <c r="AP105" t="inlineStr"/>
+      <c r="AQ105" t="inlineStr"/>
+      <c r="AR105" t="inlineStr"/>
+      <c r="AS105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>900005</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>'Olivia' poster</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons / 电影海报资料</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>900005_palette.png</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/900005_palette.png</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>近黑色、深藏蓝色、近黑色、青色、深棕色、灰青色、灰色、黄色、浅灰色</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>中低明度色调</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>蓝绿色系</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>近黑色、深藏蓝色、近黑色、青色、深棕色、灰青色、灰色、黄色、浅灰色</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>#1E2D2F</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>#2B4251</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>#0D1515</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>#48606C</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>#4C482A</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>#6F8488</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>#9CA299</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>#7B6B47</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>#D2D0CD</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>20.86%</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>18.26%</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>16.03%</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>11.82%</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>10.24%</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>9.68%</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>8.06%</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>3.86%</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>1.18%</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr"/>
+      <c r="AM106" t="inlineStr"/>
+      <c r="AN106" t="inlineStr"/>
+      <c r="AO106" t="inlineStr"/>
+      <c r="AP106" t="inlineStr"/>
+      <c r="AQ106" t="inlineStr"/>
+      <c r="AR106" t="inlineStr"/>
+      <c r="AS106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>900006</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>15 mil dibujos-343629655-large</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons / 电影海报资料</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>900006_palette.png</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/900006_palette.png</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>黑色、白色、近黑色、浅灰色、灰色、灰色、灰色、灰色、灰色</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>深色调</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>黑色系</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>黑色、白色、近黑色、浅灰色、灰色、灰色、灰色、灰色、灰色</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>#010101</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>#EBEBEB</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>#181818</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>#D0D0D0</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>#AFAFAF</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>#333333</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>#8E8E8E</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>#4F4F4F</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>#6D6D6D</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>60.08%</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>6.30%</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>6.22%</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>5.24%</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>4.86%</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>4.65%</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>4.42%</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>4.13%</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>4.10%</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr"/>
+      <c r="AL107" t="inlineStr"/>
+      <c r="AM107" t="inlineStr"/>
+      <c r="AN107" t="inlineStr"/>
+      <c r="AO107" t="inlineStr"/>
+      <c r="AP107" t="inlineStr"/>
+      <c r="AQ107" t="inlineStr"/>
+      <c r="AR107" t="inlineStr"/>
+      <c r="AS107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>900007</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>150dpiWalden A1 Poster</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons / 电影海报资料</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>900007_palette.png</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/900007_palette.png</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>黑色、黑色、近黑色、深墨绿色、深绿色、深灰绿色、灰色、灰色、浅灰色</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>深色调</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>绿色系</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>黑色、黑色、近黑色、深墨绿色、深绿色、深灰绿色、灰色、灰色、浅灰色</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>#081211</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>#030508</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>#0E211B</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>#1B3226</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>#2E4334</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>#475647</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>#646E61</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>#929693</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>#D7D8D7</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>27.54%</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>26.94%</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>17.62%</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>10.93%</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>7.50%</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>2.66%</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>0.97%</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>0.66%</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr"/>
+      <c r="AM108" t="inlineStr"/>
+      <c r="AN108" t="inlineStr"/>
+      <c r="AO108" t="inlineStr"/>
+      <c r="AP108" t="inlineStr"/>
+      <c r="AQ108" t="inlineStr"/>
+      <c r="AR108" t="inlineStr"/>
+      <c r="AS108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>900008</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1935 Sri Krishna Leelalu poster</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons / 电影海报资料</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>900008_palette.png</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/900008_palette.png</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>深灰棕色、红色、红色、鲜红色、灰红色、鲜红色、浅橙红色、浅橙红色、浅玫瑰红</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>中明度色调</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>红色系</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>深灰棕色、红色、红色、鲜红色、灰红色、鲜红色、浅橙红色、浅橙红色、浅玫瑰红</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>#584D51</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>#695257</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>#7E5556</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>#995E58</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>#816B6C</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>#A07973</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>#BC8D7F</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>#D5A28D</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>#C06556</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>21.83%</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>21.77%</t>
+        </is>
+      </c>
+      <c r="AD109" t="inlineStr">
+        <is>
+          <t>14.68%</t>
+        </is>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>8.44%</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>8.02%</t>
+        </is>
+      </c>
+      <c r="AG109" t="inlineStr">
+        <is>
+          <t>7.33%</t>
+        </is>
+      </c>
+      <c r="AH109" t="inlineStr">
+        <is>
+          <t>7.22%</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>5.39%</t>
+        </is>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>5.31%</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr"/>
+      <c r="AM109" t="inlineStr"/>
+      <c r="AN109" t="inlineStr"/>
+      <c r="AO109" t="inlineStr"/>
+      <c r="AP109" t="inlineStr"/>
+      <c r="AQ109" t="inlineStr"/>
+      <c r="AR109" t="inlineStr"/>
+      <c r="AS109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>900009</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1940, Fredric March as Jean Lafitte on original program for movie The Buccaneer</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons / 电影海报资料</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>900009_palette.png</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/900009_palette.png</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>浅米黄色、浅米黄色、浅柠檬黄、柠檬黄、金黄色、草绿色、绿色、深绿色、深绿色</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>中明度色调</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>黄色金色系</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>浅米黄色、浅米黄色、浅柠檬黄、柠檬黄、金黄色、草绿色、绿色、深绿色、深绿色</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>#EADAAA</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>#DDD0A0</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>#C9C197</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>#B7B38C</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>#A1A17F</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>#8E9172</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>#787D60</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>#5B654D</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>#3C4B37</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>21.26%</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>17.79%</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>15.01%</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>12.01%</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>10.59%</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>9.86%</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>5.50%</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>4.77%</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>3.21%</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr"/>
+      <c r="AL110" t="inlineStr"/>
+      <c r="AM110" t="inlineStr"/>
+      <c r="AN110" t="inlineStr"/>
+      <c r="AO110" t="inlineStr"/>
+      <c r="AP110" t="inlineStr"/>
+      <c r="AQ110" t="inlineStr"/>
+      <c r="AR110" t="inlineStr"/>
+      <c r="AS110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>900010</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1960 Maharathi Karna poster</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Wikimedia Commons / 电影海报资料</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>900010_palette.png</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/900010_palette.png</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>浅米黄色、浅柠檬黄、柠檬黄、金黄色、灰色、浅米黄色、灰色、深灰色、灰色</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>中明度色调</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>黄色金色系</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>浅米黄色、浅柠檬黄、柠檬黄、金黄色、灰色、浅米黄色、灰色、深灰色、灰色</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>#DAC7A5</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>#C8B89A</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>#B5A88D</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>#A19780</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>#8B8572</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>#E9D5B2</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>#757263</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>#5D5E53</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>#40453F</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>16.91%</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>13.91%</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>12.74%</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>11.88%</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>11.73%</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>10.54%</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>10.42%</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>7.84%</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr"/>
+      <c r="AL111" t="inlineStr"/>
+      <c r="AM111" t="inlineStr"/>
+      <c r="AN111" t="inlineStr"/>
+      <c r="AO111" t="inlineStr"/>
+      <c r="AP111" t="inlineStr"/>
+      <c r="AQ111" t="inlineStr"/>
+      <c r="AR111" t="inlineStr"/>
+      <c r="AS111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>met_436535</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Wheat Field with Cypresses</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Vincent van Gogh</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>1889</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>met_436535_palette.png</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_436535_palette.png</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>中低明度色调</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>绿色系</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>#849797</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>#ABADA0</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>#61828E</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>#836C2B</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>#010101</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>#485B3F</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>#697559</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>#24372C</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>#9D8746</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>20.78%</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>14.59%</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>11.69%</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>10.68%</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>10.51%</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>9.22%</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>7.85%</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>7.83%</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>6.85%</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr"/>
+      <c r="AL112" t="inlineStr"/>
+      <c r="AM112" t="inlineStr"/>
+      <c r="AN112" t="inlineStr"/>
+      <c r="AO112" t="inlineStr"/>
+      <c r="AP112" t="inlineStr"/>
+      <c r="AQ112" t="inlineStr"/>
+      <c r="AR112" t="inlineStr"/>
+      <c r="AS112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>met_436529</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>L'Arlésienne: Madame Joseph-Michel Ginoux (Marie Julien, 1848–1911)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Vincent van Gogh</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>1888–89</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>met_436529_palette.png</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_436529_palette.png</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>中明度色调</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>黄色金色系</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>#D2B138</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>#E3C754</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>#272F26</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>#354337</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>#A8C69D</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>#9E9566</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>#A0682F</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>#6D5731</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>#030201</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>21.56%</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>21.06%</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>20.85%</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>11.01%</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>7.01%</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>6.71%</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>6.05%</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>4.61%</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr"/>
+      <c r="AL113" t="inlineStr"/>
+      <c r="AM113" t="inlineStr"/>
+      <c r="AN113" t="inlineStr"/>
+      <c r="AO113" t="inlineStr"/>
+      <c r="AP113" t="inlineStr"/>
+      <c r="AQ113" t="inlineStr"/>
+      <c r="AR113" t="inlineStr"/>
+      <c r="AS113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>met_436524</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Sunflowers</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Vincent van Gogh</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>1887</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>met_436524_palette.png</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_436524_palette.png</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>中低明度色调</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>蓝色系</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>#9E8A52</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>#437384</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>#245F76</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>#5C482C</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>#786C46</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>#61909E</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>#8A661C</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>#1F3C51</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>#14171F</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>15.45%</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>13.98%</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>13.90%</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>13.76%</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>13.60%</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>9.23%</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>8.46%</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>6.98%</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>4.63%</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr"/>
+      <c r="AL114" t="inlineStr"/>
+      <c r="AM114" t="inlineStr"/>
+      <c r="AN114" t="inlineStr"/>
+      <c r="AO114" t="inlineStr"/>
+      <c r="AP114" t="inlineStr"/>
+      <c r="AQ114" t="inlineStr"/>
+      <c r="AR114" t="inlineStr"/>
+      <c r="AS114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>met_437881</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Young Woman with a Water Pitcher</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Johannes Vermeer</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ca. 1662</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>met_437881_palette.png</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_437881_palette.png</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>中低明度色调</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>棕色大地色系</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>#807B6D</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>#493D2C</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>#69685C</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>#302F28</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>#11202E</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>#1E1314</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>#624C35</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>#3E4B4E</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>#A39582</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>17.23%</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>16.51%</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>14.59%</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>12.00%</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>10.83%</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>9.43%</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>8.55%</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>5.45%</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>5.41%</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr"/>
+      <c r="AL115" t="inlineStr"/>
+      <c r="AM115" t="inlineStr"/>
+      <c r="AN115" t="inlineStr"/>
+      <c r="AO115" t="inlineStr"/>
+      <c r="AP115" t="inlineStr"/>
+      <c r="AQ115" t="inlineStr"/>
+      <c r="AR115" t="inlineStr"/>
+      <c r="AS115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>met_39799</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Under the Wave off Kanagawa (Kanagawa oki nami ura), or The Great Wave, from the series Thirty-six Views of Mount Fuji (Fugaku sanjūrokkei)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Katsushika Hokusai</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ca. 1830–32</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>met_39799_palette.png</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_39799_palette.png</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>低饱和色调</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>橙色系</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>#ECDCC1</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>#E5D0AF</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>#32455D</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>#D8C2A1</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>#C2C6B6</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>#AFAFA2</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>#41627A</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>#929691</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>#727A7D</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>26.14%</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>21.07%</t>
+        </is>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t>9.84%</t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>9.13%</t>
+        </is>
+      </c>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>8.31%</t>
+        </is>
+      </c>
+      <c r="AG116" t="inlineStr">
+        <is>
+          <t>7.42%</t>
+        </is>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>6.35%</t>
+        </is>
+      </c>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>6.22%</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>5.53%</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr"/>
+      <c r="AL116" t="inlineStr"/>
+      <c r="AM116" t="inlineStr"/>
+      <c r="AN116" t="inlineStr"/>
+      <c r="AO116" t="inlineStr"/>
+      <c r="AP116" t="inlineStr"/>
+      <c r="AQ116" t="inlineStr"/>
+      <c r="AR116" t="inlineStr"/>
+      <c r="AS116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>met_45434</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Under the Wave off Kanagawa (Kanagawa oki nami ura), also known as The Great Wave, from the series Thirty-six Views of Mount Fuji (Fugaku sanjūrokkei)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Katsushika Hokusai</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ca. 1830–32</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>met_45434_palette.png</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_45434_palette.png</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>中明度色调</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>蓝色系</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>#EAE7D4</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>#224060</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>#ECDBBA</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>#C9D3C6</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>#366282</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>#ADB4AD</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>#909796</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>#6E7C84</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>#D8C4A4</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>19.48%</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>14.47%</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>13.84%</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>11.05%</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>9.75%</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>9.63%</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>8.62%</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>7.45%</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>5.72%</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr"/>
+      <c r="AL117" t="inlineStr"/>
+      <c r="AM117" t="inlineStr"/>
+      <c r="AN117" t="inlineStr"/>
+      <c r="AO117" t="inlineStr"/>
+      <c r="AP117" t="inlineStr"/>
+      <c r="AQ117" t="inlineStr"/>
+      <c r="AR117" t="inlineStr"/>
+      <c r="AS117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>met_453064</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Page of Calligraphy from a Kalila wa Dimna</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>second quarter 16th century</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>met_453064_palette.png</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_453064_palette.png</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>中明度色调</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>橙色系</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>#A89684</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>#A38E7A</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>#AC9C90</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>#9C8670</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>#937C64</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>#856F59</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>#B2AFB0</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>#735F4A</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>#5D4A35</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>22.87%</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>19.65%</t>
+        </is>
+      </c>
+      <c r="AD118" t="inlineStr">
+        <is>
+          <t>14.76%</t>
+        </is>
+      </c>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>14.71%</t>
+        </is>
+      </c>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>10.17%</t>
+        </is>
+      </c>
+      <c r="AG118" t="inlineStr">
+        <is>
+          <t>6.47%</t>
+        </is>
+      </c>
+      <c r="AH118" t="inlineStr">
+        <is>
+          <t>5.18%</t>
+        </is>
+      </c>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>4.32%</t>
+        </is>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>1.88%</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr"/>
+      <c r="AL118" t="inlineStr"/>
+      <c r="AM118" t="inlineStr"/>
+      <c r="AN118" t="inlineStr"/>
+      <c r="AO118" t="inlineStr"/>
+      <c r="AP118" t="inlineStr"/>
+      <c r="AQ118" t="inlineStr"/>
+      <c r="AR118" t="inlineStr"/>
+      <c r="AS118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>met_465103</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Hairpin</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>200–500</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>met_465103_palette.png</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_465103_palette.png</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>高明度色调</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>蓝绿色系</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>#DEDEE1</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>#E2E2E7</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>#D8D8D9</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>#3F5149</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>#4E645D</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>#5F7972</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>#323B31</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>#76908A</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>#A0AFA9</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>39.88%</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>37.00%</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>14.89%</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>2.02%</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>1.55%</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>0.95%</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr"/>
+      <c r="AL119" t="inlineStr"/>
+      <c r="AM119" t="inlineStr"/>
+      <c r="AN119" t="inlineStr"/>
+      <c r="AO119" t="inlineStr"/>
+      <c r="AP119" t="inlineStr"/>
+      <c r="AQ119" t="inlineStr"/>
+      <c r="AR119" t="inlineStr"/>
+      <c r="AS119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>met_313439</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Seated Figure</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>6th–7th century</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>met_313439_palette.png</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_313439_palette.png</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>低饱和色调</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>绿色系</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>#A7A5A1</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>#949492</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>#BFC0BB</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>#D6D7D7</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>#E8E9E8</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>#6D8C72</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>#4C6554</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>#303A38</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>#855D3F</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>29.32%</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>22.04%</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>14.12%</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>10.34%</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>8.42%</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>6.02%</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>4.89%</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>2.89%</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>1.96%</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr"/>
+      <c r="AL120" t="inlineStr"/>
+      <c r="AM120" t="inlineStr"/>
+      <c r="AN120" t="inlineStr"/>
+      <c r="AO120" t="inlineStr"/>
+      <c r="AP120" t="inlineStr"/>
+      <c r="AQ120" t="inlineStr"/>
+      <c r="AR120" t="inlineStr"/>
+      <c r="AS120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>met_437394</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Aristotle with a Bust of Homer</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Rembrandt (Rembrandt van Rijn)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>1653</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>met_437394_palette.png</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_437394_palette.png</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>深色调</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>棕色大地色系</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>#080403</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>#0F0806</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>#180F09</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>#24170D</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>#301F11</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>#3E2B18</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>#513C23</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>#685235</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>#866E4D</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>39.34%</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>22.16%</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>12.76%</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>9.94%</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>7.47%</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>2.27%</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr"/>
+      <c r="AL121" t="inlineStr"/>
+      <c r="AM121" t="inlineStr"/>
+      <c r="AN121" t="inlineStr"/>
+      <c r="AO121" t="inlineStr"/>
+      <c r="AP121" t="inlineStr"/>
+      <c r="AQ121" t="inlineStr"/>
+      <c r="AR121" t="inlineStr"/>
+      <c r="AS121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>met_11417</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Washington Crossing the Delaware</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Emanuel Leutze</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>met_11417_palette.png</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_11417_palette.png</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>中低明度色调</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>棕色大地色系</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>#686555</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>#332C25</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>#4C3D2E</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>#82785E</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>#63533C</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>#9D9074</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>#BFAF91</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>#DCCDA4</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>#070606</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>18.05%</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>16.71%</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>11.84%</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>10.94%</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>8.30%</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>6.70%</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>1.63%</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr"/>
+      <c r="AL122" t="inlineStr"/>
+      <c r="AM122" t="inlineStr"/>
+      <c r="AN122" t="inlineStr"/>
+      <c r="AO122" t="inlineStr"/>
+      <c r="AP122" t="inlineStr"/>
+      <c r="AQ122" t="inlineStr"/>
+      <c r="AR122" t="inlineStr"/>
+      <c r="AS122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>met_436965</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>The Monet Family in Their Garden at Argenteuil</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Edouard Manet</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>1874</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>met_436965_palette.png</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_436965_palette.png</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>中低明度色调</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>绿色系</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>#45523A</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>#4B6B52</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>#303D2F</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>#325B45</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>#000000</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>#635C41</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>#6E755C</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>#B6AC9C</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>#888C83</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>23.46%</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>16.59%</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>11.92%</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>11.48%</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>11.38%</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>8.24%</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>7.07%</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>5.34%</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>4.51%</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr"/>
+      <c r="AL123" t="inlineStr"/>
+      <c r="AM123" t="inlineStr"/>
+      <c r="AN123" t="inlineStr"/>
+      <c r="AO123" t="inlineStr"/>
+      <c r="AP123" t="inlineStr"/>
+      <c r="AQ123" t="inlineStr"/>
+      <c r="AR123" t="inlineStr"/>
+      <c r="AS123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>met_40278</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Meeting between Yaoshan and Li Ao</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Zhiweng</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>before 1256</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>met_40278_palette.png</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_40278_palette.png</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>中明度色调</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>橙色系</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>#A28963</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>#9D845E</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>#A78F67</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>#967D59</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>#8D7554</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>#826D4E</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>#766348</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>#675841</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>#524839</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>27.27%</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>21.11%</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>15.34%</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>10.94%</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>8.45%</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>6.80%</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>5.08%</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>3.68%</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>1.35%</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr"/>
+      <c r="AL124" t="inlineStr"/>
+      <c r="AM124" t="inlineStr"/>
+      <c r="AN124" t="inlineStr"/>
+      <c r="AO124" t="inlineStr"/>
+      <c r="AP124" t="inlineStr"/>
+      <c r="AQ124" t="inlineStr"/>
+      <c r="AR124" t="inlineStr"/>
+      <c r="AS124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>met_45308</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>The Umegawa at Ryogoku Yanagibashi</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Utagawa Hiroshige</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>ca. 1835–42</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>met_45308_palette.png</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>/Users/emilylee/Downloads/后端 3/paletteseek_backend/color_cards/met_45308_palette.png</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>中明度色调</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>橙色系</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>#786962</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>#615853</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>#648884</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>#E7D3B9</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>#586D6E</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>#D6B999</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>#A8826C</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>#364C60</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>#A0A8A1</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>21.15%</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>17.62%</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>13.34%</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>11.87%</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>11.05%</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>9.51%</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>7.97%</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>4.58%</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>2.92%</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr"/>
+      <c r="AL125" t="inlineStr"/>
+      <c r="AM125" t="inlineStr"/>
+      <c r="AN125" t="inlineStr"/>
+      <c r="AO125" t="inlineStr"/>
+      <c r="AP125" t="inlineStr"/>
+      <c r="AQ125" t="inlineStr"/>
+      <c r="AR125" t="inlineStr"/>
+      <c r="AS125" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23193,8 +27045,10 @@
           <t>输入作品数量</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>100</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -23208,8 +27062,10 @@
           <t>成功生成数量</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>100</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -23223,8 +27079,10 @@
           <t>色卡图片数量</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>100</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -23238,8 +27096,10 @@
           <t>失败数量</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
